--- a/workflows/daily-report-generate-flow/out/经营日报.xlsx
+++ b/workflows/daily-report-generate-flow/out/经营日报.xlsx
@@ -679,13 +679,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,63 +691,11 @@
           <t>项</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>值</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>明细</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>处理</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>区间内缺失日期</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1 天</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>未补零；环比在缺失处断开，不得跨缺口比较，否则会制造假跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>单日样本量不足</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-27（15 单）</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>转化率 0.8%、退款率 12.72%</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>订单 &lt; 20 单，转化率与退款率失真 —— 只报值不下结论</t>
+          <t>（无）</t>
         </is>
       </c>
     </row>

--- a/workflows/daily-report-generate-flow/out/经营日报.xlsx
+++ b/workflows/daily-report-generate-flow/out/经营日报.xlsx
@@ -679,10 +679,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -691,11 +694,63 @@
           <t>项</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>明细</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>处理</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>（无）</t>
+          <t>区间内缺失日期</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1 天</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>未补零；环比在缺失处断开，不得跨缺口比较，否则会制造假跌</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>单日样本量不足</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-27（15 单）</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>转化率 0.8%、退款率 12.72%</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>订单 &lt; 20 单，转化率与退款率失真 —— 只报值不下结论</t>
         </is>
       </c>
     </row>
